--- a/product_selector_out/STM32F7x3.xlsx
+++ b/product_selector_out/STM32F7x3.xlsx
@@ -7803,7 +7803,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the footnote qualifies the figure</t>
+          <t>Table 16. General operating conditions (continued): V_DD min reads '1.7(3)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F7x3.xlsx
+++ b/product_selector_out/STM32F7x3.xlsx
@@ -3834,7 +3834,7 @@
       </c>
       <c r="AA20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="4" t="inlineStr">
@@ -4771,9 +4771,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="9" t="inlineStr">
@@ -5108,9 +5108,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="9" t="inlineStr">
@@ -5445,9 +5445,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="9" t="inlineStr">
@@ -5782,9 +5782,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="9" t="inlineStr">
@@ -6119,9 +6119,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="9" t="inlineStr">
@@ -6456,9 +6456,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="9" t="inlineStr">
@@ -6793,9 +6793,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="9" t="inlineStr">
@@ -7130,9 +7130,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="9" t="inlineStr">
@@ -7467,9 +7467,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="9" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="AA20" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="9" t="inlineStr">

--- a/product_selector_out/STM32F7x3.xlsx
+++ b/product_selector_out/STM32F7x3.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO20"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.390625" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -907,6 +908,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1004,6 +1010,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1338,6 +1345,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f732ie.pdf</t>
         </is>
       </c>
@@ -1675,6 +1687,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -2012,6 +2029,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f732ie.pdf</t>
         </is>
       </c>
@@ -2349,6 +2371,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -2686,6 +2713,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -3023,6 +3055,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -3360,6 +3397,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
@@ -3697,6 +3739,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f732ie.pdf</t>
         </is>
       </c>
@@ -4034,12 +4081,17 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f722ic.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -4062,12 +4114,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -4082,9 +4136,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -4129,7 +4182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO20"/>
+  <dimension ref="A1:BP20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4199,6 +4252,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4542,6 +4596,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -4639,6 +4698,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4971,7 +5031,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5308,7 +5373,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5645,7 +5715,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -5982,7 +6057,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6319,7 +6399,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6656,7 +6741,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6993,7 +7083,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7330,7 +7425,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7667,7 +7767,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7675,8 +7780,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
